--- a/artfynd/A 8929-2023 artfynd.xlsx
+++ b/artfynd/A 8929-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8929-2023 artfynd.xlsx
+++ b/artfynd/A 8929-2023 artfynd.xlsx
@@ -1589,7 +1589,7 @@
         <v>119925205</v>
       </c>
       <c r="B10" t="n">
-        <v>58177</v>
+        <v>58187</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 8929-2023 artfynd.xlsx
+++ b/artfynd/A 8929-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66712378</v>
+        <v>104401590</v>
       </c>
       <c r="B2" t="n">
-        <v>55981</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,44 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102964</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tomtebyholm, Harby, Sm</t>
+          <t>Öst Harbymo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571446.3414444982</v>
+        <v>571679</v>
       </c>
       <c r="R2" t="n">
-        <v>6282987.274203516</v>
+        <v>6283075</v>
       </c>
       <c r="S2" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,22 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-07-14</t>
+          <t>2022-10-31</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-07-14</t>
+          <t>2022-10-31</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,76 +771,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hugo Johansson</t>
+          <t>Sandra Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hugo Johansson</t>
+          <t>Sandra Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>71534119</v>
+        <v>113017545</v>
       </c>
       <c r="B3" t="n">
-        <v>55803</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102952</v>
+        <v>366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Vanellus vanellus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tomtebyholm, Harby, Sm</t>
+          <t>Tomtebyholm, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571446.3414444982</v>
+        <v>571674</v>
       </c>
       <c r="R3" t="n">
-        <v>6282987.274203516</v>
+        <v>6283075</v>
       </c>
       <c r="S3" t="n">
-        <v>125</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,22 +848,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-05-25</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-05-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,69 +862,61 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hugo Johansson</t>
+          <t>Elin Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hugo Johansson</t>
+          <t>Elin Jonsson, Julia Odéhn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73669062</v>
+        <v>82286714</v>
       </c>
       <c r="B4" t="n">
-        <v>55978</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56925</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102966</v>
+        <v>100045</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Larus argentatus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pontoppidan, 1763</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -969,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571446.3414444982</v>
+        <v>571446</v>
       </c>
       <c r="R4" t="n">
-        <v>6282987.274203516</v>
+        <v>6282987</v>
       </c>
       <c r="S4" t="n">
         <v>125</v>
@@ -999,22 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-10-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-02-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-10-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-02-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,54 +986,60 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104401590</v>
+        <v>82286560</v>
       </c>
       <c r="B5" t="n">
-        <v>90138</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>366</v>
+        <v>100065</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öst Harbymo, Sm</t>
+          <t>Tomtebyholm, Harby, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571679.3261569249</v>
+        <v>571446</v>
       </c>
       <c r="R5" t="n">
-        <v>6283074.73736036</v>
+        <v>6282987</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,22 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>08:49</t>
+          <t>2020-02-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>08:49</t>
+          <t>2020-02-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,62 +1083,74 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sandra Nilsson</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sandra Nilsson</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113017540</v>
+        <v>113017537</v>
       </c>
       <c r="B6" t="n">
-        <v>100636</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221317</v>
+        <v>100070</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tomtebyholm, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571210</v>
+        <v>571114</v>
       </c>
       <c r="R6" t="n">
-        <v>6282732</v>
+        <v>6282999</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1224,12 +1177,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-08-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Unga individer</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,6 +1196,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1249,74 +1208,52 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Jonsson, Julia Odéhn</t>
+          <t>Göran Holm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113017537</v>
+        <v>113017538</v>
       </c>
       <c r="B7" t="n">
-        <v>55967</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100070</v>
+        <v>100088</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tomtebyholm, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571114</v>
+        <v>571100</v>
       </c>
       <c r="R7" t="n">
-        <v>6282999</v>
+        <v>6282967</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1343,17 +1280,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Unga individer</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,7 +1294,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1374,22 +1305,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Holm</t>
+          <t>Elin Jonsson, Julia Odéhn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113017538</v>
+        <v>119925205</v>
       </c>
       <c r="B8" t="n">
-        <v>57512</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,37 +1323,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100088</v>
+        <v>100141</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tomtebyholm, Sm</t>
+          <t>sandtaget, Harby, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571100</v>
+        <v>571121</v>
       </c>
       <c r="R8" t="n">
-        <v>6282967</v>
+        <v>6282994</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1451,12 +1386,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Minst ett tjugotal salamandrar i vattnet i sandtaget. Flera av dom säkert bestämda till större vattensalamander.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,71 +1405,78 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Elin Jonsson</t>
+          <t>Göran Holm</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elin Jonsson, Julia Odéhn</t>
+          <t>Göran Holm</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113017545</v>
+        <v>71534119</v>
       </c>
       <c r="B9" t="n">
-        <v>90791</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57317</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>366</v>
+        <v>102952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Vanellus vanellus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tomtebyholm, Sm</t>
+          <t>Tomtebyholm, Harby, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571674</v>
+        <v>571446</v>
       </c>
       <c r="R9" t="n">
-        <v>6283075</v>
+        <v>6282987</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>125</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1553,12 +1500,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2018-05-25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2018-05-25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1567,81 +1514,78 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elin Jonsson</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elin Jonsson, Julia Odéhn</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119925205</v>
+        <v>73669062</v>
       </c>
       <c r="B10" t="n">
-        <v>58187</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57563</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100141</v>
+        <v>102966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Larus argentatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>Pontoppidan, 1763</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>sandtaget, Harby, Sm</t>
+          <t>Tomtebyholm, Harby, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571121</v>
+        <v>571446</v>
       </c>
       <c r="R10" t="n">
-        <v>6282994</v>
+        <v>6282987</v>
       </c>
       <c r="S10" t="n">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1665,17 +1609,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2018-10-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Minst ett tjugotal salamandrar i vattnet i sandtaget. Flera av dom säkert bestämda till större vattensalamander.</t>
+          <t>2018-10-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1684,22 +1623,222 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Göran Holm</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Göran Holm</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>66712380</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58209</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102980</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ladusvala</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hirundo rustica</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tomtebyholm, Harby, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>571446</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6282987</v>
+      </c>
+      <c r="S11" t="n">
+        <v>125</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2017-07-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2017-07-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>113017540</v>
+      </c>
+      <c r="B12" t="n">
+        <v>102419</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221317</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gullklöver</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Trifolium aureum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tomtebyholm, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>571209</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6282731</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Elin Jonsson, Julia Odéhn</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8929-2023 artfynd.xlsx
+++ b/artfynd/A 8929-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104401590</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113017545</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82286714</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82286560</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113017537</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1309,6 +1339,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113017538</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119925205</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1529,6 +1569,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71534119</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1638,6 +1683,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73669062</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66712380</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1839,8 +1894,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113017540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>